--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136171550</v>
       </c>
       <c r="B4" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136171550</v>
       </c>
       <c r="B4" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136171550</v>
       </c>
       <c r="B4" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48880-2023 artfynd.xlsx
+++ b/artfynd/A 48880-2023 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>136171550</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
